--- a/src/test/resources/data/data.xlsx
+++ b/src/test/resources/data/data.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\saucedemo\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\sauceDemo\src\test\resources\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D025B487-FDC9-469A-8138-85CC838B6D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B96487-A779-4E9C-B559-F3874097EE46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2490" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,67 +25,62 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+  <si>
+    <t>Username and password do not match any user in this service</t>
+  </si>
+  <si>
+    <t>locked_out_user</t>
+  </si>
+  <si>
+    <t>standard_user</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>Cano</t>
+  </si>
+  <si>
+    <t>Camila</t>
+  </si>
+  <si>
+    <t>secret_sauce</t>
+  </si>
+  <si>
+    <t>Thank you for your order!</t>
+  </si>
+  <si>
+    <t>Castaño</t>
+  </si>
+  <si>
+    <t>Lucas</t>
+  </si>
+  <si>
+    <t>validation</t>
+  </si>
+  <si>
+    <t>postal_code</t>
+  </si>
+  <si>
+    <t>last_name</t>
+  </si>
+  <si>
+    <t>first_name</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
   <si>
     <t>username</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>last_name</t>
-  </si>
-  <si>
-    <t>postal_code</t>
-  </si>
-  <si>
-    <t>validation</t>
-  </si>
-  <si>
-    <t>standard_user</t>
-  </si>
-  <si>
-    <t>secret_sauce</t>
-  </si>
-  <si>
-    <t>Lucas</t>
-  </si>
-  <si>
-    <t>Castaño</t>
-  </si>
-  <si>
-    <t>Thank you for your order!</t>
-  </si>
-  <si>
-    <t>first_name</t>
-  </si>
-  <si>
-    <t>Alejandro</t>
-  </si>
-  <si>
-    <t>González</t>
-  </si>
-  <si>
-    <t>Camila</t>
-  </si>
-  <si>
-    <t>Cano</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -113,9 +108,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,44 +392,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.7109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
         <v>10</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -444,47 +430,35 @@
         <v>34584</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3">
-        <v>54530</v>
+        <v>4</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4">
-        <v>54354</v>
+        <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
